--- a/data/1.영업구역별_주소현행화20260304.xlsx
+++ b/data/1.영업구역별_주소현행화20260304.xlsx
@@ -460,7 +460,7 @@
     <t>김태형</t>
   </si>
   <si>
-    <t>고승남</t>
+    <t>안근영</t>
   </si>
   <si>
     <t>최용호</t>
